--- a/tests/fixtures/2020-2025 Political-Related Sexual Violence Incident Data.xlsx
+++ b/tests/fixtures/2020-2025 Political-Related Sexual Violence Incident Data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4950" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4944" uniqueCount="816">
   <si>
     <t>Date</t>
   </si>
@@ -1538,12 +1538,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unspecified Sexual Violence </t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>119228</t>
@@ -2939,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="V2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W2" s="1">
         <v>45957</v>
@@ -3007,7 +3001,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="W3" s="1">
         <v>45942</v>
@@ -3075,7 +3069,7 @@
         <v>1</v>
       </c>
       <c r="V4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="W4" s="1">
         <v>45943</v>
@@ -3143,7 +3137,7 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="W5" s="1">
         <v>45943</v>
@@ -3211,7 +3205,7 @@
         <v>1</v>
       </c>
       <c r="V6" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W6" s="1">
         <v>45936</v>
@@ -3279,7 +3273,7 @@
         <v>1</v>
       </c>
       <c r="V7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="W7" s="1">
         <v>45940</v>
@@ -3347,7 +3341,7 @@
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="W8" s="1">
         <v>45935</v>
@@ -3415,7 +3409,7 @@
         <v>1</v>
       </c>
       <c r="V9" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="W9" s="1">
         <v>45940</v>
@@ -3483,7 +3477,7 @@
         <v>1</v>
       </c>
       <c r="V10" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="W10" s="1">
         <v>45943</v>
@@ -3551,7 +3545,7 @@
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="W11" s="1">
         <v>45935</v>
@@ -3619,7 +3613,7 @@
         <v>2</v>
       </c>
       <c r="V12" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="W12" s="1">
         <v>45943</v>
@@ -3687,7 +3681,7 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="W13" s="1">
         <v>45935</v>
@@ -3755,7 +3749,7 @@
         <v>4</v>
       </c>
       <c r="V14" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="W14" s="1">
         <v>45943</v>
@@ -3823,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="W15" s="1">
         <v>45900</v>
@@ -3891,7 +3885,7 @@
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W16" s="1">
         <v>45943</v>
@@ -3959,7 +3953,7 @@
         <v>70</v>
       </c>
       <c r="V17" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="W17" s="1">
         <v>45867</v>
@@ -4027,7 +4021,7 @@
         <v>6</v>
       </c>
       <c r="V18" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="W18" s="1">
         <v>45865</v>
@@ -4095,7 +4089,7 @@
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="W19" s="1">
         <v>45865</v>
@@ -4163,7 +4157,7 @@
         <v>3</v>
       </c>
       <c r="V20" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="W20" s="1">
         <v>45865</v>
@@ -4231,7 +4225,7 @@
         <v>90</v>
       </c>
       <c r="V21" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="W21" s="1">
         <v>45856</v>
@@ -4299,7 +4293,7 @@
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="W22" s="1">
         <v>45865</v>
@@ -4367,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="V23" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="W23" s="1">
         <v>45865</v>
@@ -4435,7 +4429,7 @@
         <v>1</v>
       </c>
       <c r="V24" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="W24" s="1">
         <v>45858</v>
@@ -4503,7 +4497,7 @@
         <v>2</v>
       </c>
       <c r="V25" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="W25" s="1">
         <v>45858</v>
@@ -4571,7 +4565,7 @@
         <v>1</v>
       </c>
       <c r="V26" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="W26" s="1">
         <v>45858</v>
@@ -4639,7 +4633,7 @@
         <v>1</v>
       </c>
       <c r="V27" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="W27" s="1">
         <v>45822</v>
@@ -4707,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="V28" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="W28" s="1">
         <v>45822</v>
@@ -4775,7 +4769,7 @@
         <v>1</v>
       </c>
       <c r="V29" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="W29" s="1">
         <v>45809</v>
@@ -4843,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="V30" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="W30" s="1">
         <v>45810</v>
@@ -4911,7 +4905,7 @@
         <v>1</v>
       </c>
       <c r="V31" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="W31" s="1">
         <v>45810</v>
@@ -4979,7 +4973,7 @@
         <v>1</v>
       </c>
       <c r="V32" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="W32" s="1">
         <v>45809</v>
@@ -5047,7 +5041,7 @@
         <v>1</v>
       </c>
       <c r="V33" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="W33" s="1">
         <v>45810</v>
@@ -5115,7 +5109,7 @@
         <v>2</v>
       </c>
       <c r="V34" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="W34" s="1">
         <v>45804</v>
@@ -5183,7 +5177,7 @@
         <v>1</v>
       </c>
       <c r="V35" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="W35" s="1">
         <v>45810</v>
@@ -5248,7 +5242,7 @@
         <v>1</v>
       </c>
       <c r="V36" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="W36" s="1">
         <v>45795</v>
@@ -5316,7 +5310,7 @@
         <v>1</v>
       </c>
       <c r="V37" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="W37" s="1">
         <v>45795</v>
@@ -5384,7 +5378,7 @@
         <v>2</v>
       </c>
       <c r="V38" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="W38" s="1">
         <v>45753</v>
@@ -5452,7 +5446,7 @@
         <v>1</v>
       </c>
       <c r="V39" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="W39" s="1">
         <v>45741</v>
@@ -5520,7 +5514,7 @@
         <v>1</v>
       </c>
       <c r="V40" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="W40" s="1">
         <v>45746</v>
@@ -5588,7 +5582,7 @@
         <v>1</v>
       </c>
       <c r="V41" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="W41" s="1">
         <v>45746</v>
@@ -5656,7 +5650,7 @@
         <v>1</v>
       </c>
       <c r="V42" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="W42" s="1">
         <v>45746</v>
@@ -5724,7 +5718,7 @@
         <v>1</v>
       </c>
       <c r="V43" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="W43" s="1">
         <v>45727</v>
@@ -5792,7 +5786,7 @@
         <v>1</v>
       </c>
       <c r="V44" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="W44" s="1">
         <v>45726</v>
@@ -5860,7 +5854,7 @@
         <v>1</v>
       </c>
       <c r="V45" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="W45" s="1">
         <v>45725</v>
@@ -5928,7 +5922,7 @@
         <v>1</v>
       </c>
       <c r="V46" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="W46" s="1">
         <v>45726</v>
@@ -5996,7 +5990,7 @@
         <v>1</v>
       </c>
       <c r="V47" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="W47" s="1">
         <v>45726</v>
@@ -6064,7 +6058,7 @@
         <v>1</v>
       </c>
       <c r="V48" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="W48" s="1">
         <v>45726</v>
@@ -6132,7 +6126,7 @@
         <v>1</v>
       </c>
       <c r="V49" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="W49" s="1">
         <v>45726</v>
@@ -6200,7 +6194,7 @@
         <v>1</v>
       </c>
       <c r="V50" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="W50" s="1">
         <v>45726</v>
@@ -6268,7 +6262,7 @@
         <v>1</v>
       </c>
       <c r="V51" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="W51" s="1">
         <v>45684</v>
@@ -6336,7 +6330,7 @@
         <v>1</v>
       </c>
       <c r="V52" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="W52" s="1">
         <v>45684</v>
@@ -6404,7 +6398,7 @@
         <v>1</v>
       </c>
       <c r="V53" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="W53" s="1">
         <v>45684</v>
@@ -6472,7 +6466,7 @@
         <v>1</v>
       </c>
       <c r="V54" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="W54" s="1">
         <v>45693</v>
@@ -6540,7 +6534,7 @@
         <v>1</v>
       </c>
       <c r="V55" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="W55" s="1">
         <v>45692</v>
@@ -6608,7 +6602,7 @@
         <v>1</v>
       </c>
       <c r="V56" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="W56" s="1">
         <v>45689</v>
@@ -6676,7 +6670,7 @@
         <v>1</v>
       </c>
       <c r="V57" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="W57" s="1">
         <v>45671</v>
@@ -6744,7 +6738,7 @@
         <v>1</v>
       </c>
       <c r="V58" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="W58" s="1">
         <v>45693</v>
@@ -6812,7 +6806,7 @@
         <v>1</v>
       </c>
       <c r="V59" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="W59" s="1">
         <v>45690</v>
@@ -6880,7 +6874,7 @@
         <v>2</v>
       </c>
       <c r="V60" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="W60" s="1">
         <v>45633</v>
@@ -6948,7 +6942,7 @@
         <v>1</v>
       </c>
       <c r="V61" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="W61" s="1">
         <v>45633</v>
@@ -7016,7 +7010,7 @@
         <v>1</v>
       </c>
       <c r="V62" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="W62" s="1">
         <v>45689</v>
@@ -7084,7 +7078,7 @@
         <v>1</v>
       </c>
       <c r="V63" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="W63" s="1">
         <v>45629</v>
@@ -7152,7 +7146,7 @@
         <v>1</v>
       </c>
       <c r="V64" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="W64" s="1">
         <v>45690</v>
@@ -7220,7 +7214,7 @@
         <v>1</v>
       </c>
       <c r="V65" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W65" s="1">
         <v>45634</v>
@@ -7288,7 +7282,7 @@
         <v>1</v>
       </c>
       <c r="V66" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="W66" s="1">
         <v>45605</v>
@@ -7356,7 +7350,7 @@
         <v>1</v>
       </c>
       <c r="V67" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="W67" s="1">
         <v>45725</v>
@@ -7424,7 +7418,7 @@
         <v>1</v>
       </c>
       <c r="V68" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="W68" s="1">
         <v>45605</v>
@@ -7492,7 +7486,7 @@
         <v>1</v>
       </c>
       <c r="V69" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="W69" s="1">
         <v>45608</v>
@@ -7560,7 +7554,7 @@
         <v>1</v>
       </c>
       <c r="V70" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="W70" s="1">
         <v>45612</v>
@@ -7628,7 +7622,7 @@
         <v>1</v>
       </c>
       <c r="V71" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="W71" s="1">
         <v>45605</v>
@@ -7696,7 +7690,7 @@
         <v>1</v>
       </c>
       <c r="V72" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="W72" s="1">
         <v>45605</v>
@@ -7764,7 +7758,7 @@
         <v>1</v>
       </c>
       <c r="V73" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="W73" s="1">
         <v>45606</v>
@@ -7832,7 +7826,7 @@
         <v>1</v>
       </c>
       <c r="V74" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="W74" s="1">
         <v>45612</v>
@@ -7900,7 +7894,7 @@
         <v>1</v>
       </c>
       <c r="V75" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="W75" s="1">
         <v>45604</v>
@@ -7968,7 +7962,7 @@
         <v>1</v>
       </c>
       <c r="V76" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="W76" s="1">
         <v>45569</v>
@@ -8036,7 +8030,7 @@
         <v>2</v>
       </c>
       <c r="V77" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="W77" s="1">
         <v>45570</v>
@@ -8104,7 +8098,7 @@
         <v>1</v>
       </c>
       <c r="V78" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="W78" s="1">
         <v>45557</v>
@@ -8172,7 +8166,7 @@
         <v>1</v>
       </c>
       <c r="V79" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="W79" s="1">
         <v>45512</v>
@@ -8240,7 +8234,7 @@
         <v>3</v>
       </c>
       <c r="V80" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="W80" s="1">
         <v>45504</v>
@@ -8308,7 +8302,7 @@
         <v>1</v>
       </c>
       <c r="V81" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="W81" s="1">
         <v>45504</v>
@@ -8376,7 +8370,7 @@
         <v>1</v>
       </c>
       <c r="V82" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="W82" s="1">
         <v>45507</v>
@@ -8444,7 +8438,7 @@
         <v>1</v>
       </c>
       <c r="V83" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="W83" s="1">
         <v>45515</v>
@@ -8512,7 +8506,7 @@
         <v>1</v>
       </c>
       <c r="V84" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="W84" s="1">
         <v>45512</v>
@@ -8580,7 +8574,7 @@
         <v>1</v>
       </c>
       <c r="V85" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="W85" s="1">
         <v>45513</v>
@@ -8648,7 +8642,7 @@
         <v>2</v>
       </c>
       <c r="V86" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="W86" s="1">
         <v>45512</v>
@@ -8716,7 +8710,7 @@
         <v>1</v>
       </c>
       <c r="V87" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="W87" s="1">
         <v>45512</v>
@@ -8784,7 +8778,7 @@
         <v>1</v>
       </c>
       <c r="V88" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="W88" s="1">
         <v>45512</v>
@@ -8852,7 +8846,7 @@
         <v>1</v>
       </c>
       <c r="V89" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="W89" s="1">
         <v>45480</v>
@@ -8920,7 +8914,7 @@
         <v>1</v>
       </c>
       <c r="V90" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="W90" s="1">
         <v>45488</v>
@@ -8988,7 +8982,7 @@
         <v>1</v>
       </c>
       <c r="V91" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="W91" s="1">
         <v>45488</v>
@@ -9056,7 +9050,7 @@
         <v>2</v>
       </c>
       <c r="V92" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="W92" s="1">
         <v>45489</v>
@@ -9124,7 +9118,7 @@
         <v>1</v>
       </c>
       <c r="V93" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="W93" s="1">
         <v>45606</v>
@@ -9192,7 +9186,7 @@
         <v>8</v>
       </c>
       <c r="V94" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="W94" s="1">
         <v>45450</v>
@@ -9260,7 +9254,7 @@
         <v>1</v>
       </c>
       <c r="V95" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="W95" s="1">
         <v>45460</v>
@@ -9328,7 +9322,7 @@
         <v>1</v>
       </c>
       <c r="V96" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="W96" s="1">
         <v>45461</v>
@@ -9396,7 +9390,7 @@
         <v>1</v>
       </c>
       <c r="V97" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="W97" s="1">
         <v>45443</v>
@@ -9464,7 +9458,7 @@
         <v>1</v>
       </c>
       <c r="V98" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="W98" s="1">
         <v>45445</v>
@@ -9532,7 +9526,7 @@
         <v>1</v>
       </c>
       <c r="V99" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="W99" s="1">
         <v>45442</v>
@@ -9600,7 +9594,7 @@
         <v>1</v>
       </c>
       <c r="V100" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="W100" s="1">
         <v>45419</v>
@@ -9668,7 +9662,7 @@
         <v>1</v>
       </c>
       <c r="V101" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="W101" s="1">
         <v>45426</v>
@@ -9736,7 +9730,7 @@
         <v>1</v>
       </c>
       <c r="V102" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="W102" s="1">
         <v>45418</v>
@@ -9804,7 +9798,7 @@
         <v>1</v>
       </c>
       <c r="V103" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="W103" s="1">
         <v>45418</v>
@@ -9872,7 +9866,7 @@
         <v>1</v>
       </c>
       <c r="V104" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="W104" s="1">
         <v>45418</v>
@@ -9940,7 +9934,7 @@
         <v>70</v>
       </c>
       <c r="V105" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="W105" s="1">
         <v>45424</v>
@@ -10008,7 +10002,7 @@
         <v>1</v>
       </c>
       <c r="V106" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="W106" s="1">
         <v>45375</v>
@@ -10076,7 +10070,7 @@
         <v>1</v>
       </c>
       <c r="V107" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="W107" s="1">
         <v>45418</v>
@@ -10144,7 +10138,7 @@
         <v>1</v>
       </c>
       <c r="V108" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="W108" s="1">
         <v>45375</v>
@@ -10212,7 +10206,7 @@
         <v>1</v>
       </c>
       <c r="V109" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="W109" s="1">
         <v>45419</v>
@@ -10280,7 +10274,7 @@
         <v>1</v>
       </c>
       <c r="V110" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="W110" s="1">
         <v>45367</v>
@@ -10348,7 +10342,7 @@
         <v>1</v>
       </c>
       <c r="V111" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="W111" s="1">
         <v>45361</v>
@@ -10416,7 +10410,7 @@
         <v>10</v>
       </c>
       <c r="V112" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="W112" s="1">
         <v>45361</v>
@@ -10484,7 +10478,7 @@
         <v>1</v>
       </c>
       <c r="V113" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="W113" s="1">
         <v>45364</v>
@@ -10552,7 +10546,7 @@
         <v>1</v>
       </c>
       <c r="V114" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="W114" s="1">
         <v>45511</v>
@@ -10620,7 +10614,7 @@
         <v>1</v>
       </c>
       <c r="V115" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="W115" s="1">
         <v>45353</v>
@@ -10688,7 +10682,7 @@
         <v>1</v>
       </c>
       <c r="V116" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="W116" s="1">
         <v>45351</v>
@@ -10756,7 +10750,7 @@
         <v>200</v>
       </c>
       <c r="V117" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="W117" s="1">
         <v>45810</v>
@@ -10824,7 +10818,7 @@
         <v>1</v>
       </c>
       <c r="V118" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="W118" s="1">
         <v>45334</v>
@@ -10892,7 +10886,7 @@
         <v>1</v>
       </c>
       <c r="V119" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="W119" s="1">
         <v>45334</v>
@@ -10960,7 +10954,7 @@
         <v>1</v>
       </c>
       <c r="V120" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="W120" s="1">
         <v>45334</v>
@@ -11028,7 +11022,7 @@
         <v>1</v>
       </c>
       <c r="V121" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="W121" s="1">
         <v>45337</v>
@@ -11096,7 +11090,7 @@
         <v>1</v>
       </c>
       <c r="V122" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="W122" s="1">
         <v>45337</v>
@@ -11164,7 +11158,7 @@
         <v>1</v>
       </c>
       <c r="V123" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="W123" s="1">
         <v>45337</v>
@@ -11232,7 +11226,7 @@
         <v>1</v>
       </c>
       <c r="V124" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="W124" s="1">
         <v>45337</v>
@@ -11300,7 +11294,7 @@
         <v>2</v>
       </c>
       <c r="V125" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="W125" s="1">
         <v>45337</v>
@@ -11368,7 +11362,7 @@
         <v>1</v>
       </c>
       <c r="V126" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="W126" s="1">
         <v>45334</v>
@@ -11436,7 +11430,7 @@
         <v>1</v>
       </c>
       <c r="V127" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="W127" s="1">
         <v>45347</v>
@@ -11504,7 +11498,7 @@
         <v>1</v>
       </c>
       <c r="V128" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="W128" s="1">
         <v>45344</v>
@@ -11572,7 +11566,7 @@
         <v>1</v>
       </c>
       <c r="V129" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="W129" s="1">
         <v>45344</v>
@@ -11640,7 +11634,7 @@
         <v>1</v>
       </c>
       <c r="V130" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="W130" s="1">
         <v>45376</v>
@@ -11705,7 +11699,7 @@
         <v>1</v>
       </c>
       <c r="V131" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="W131" s="1">
         <v>45378</v>
@@ -11773,7 +11767,7 @@
         <v>1</v>
       </c>
       <c r="V132" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="W132" s="1">
         <v>45378</v>
@@ -11841,7 +11835,7 @@
         <v>1</v>
       </c>
       <c r="V133" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="W133" s="1">
         <v>45223</v>
@@ -11909,7 +11903,7 @@
         <v>1</v>
       </c>
       <c r="V134" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="W134" s="1">
         <v>45376</v>
@@ -11977,7 +11971,7 @@
         <v>1</v>
       </c>
       <c r="V135" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="W135" s="1">
         <v>45335</v>
@@ -12045,7 +12039,7 @@
         <v>1</v>
       </c>
       <c r="V136" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="W136" s="1">
         <v>45377</v>
@@ -12113,7 +12107,7 @@
         <v>1</v>
       </c>
       <c r="V137" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="W137" s="1">
         <v>45335</v>
@@ -12172,7 +12166,7 @@
         <v>1</v>
       </c>
       <c r="V138" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="W138" s="1">
         <v>45376</v>
@@ -12240,7 +12234,7 @@
         <v>1</v>
       </c>
       <c r="V139" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="W139" s="1">
         <v>45427</v>
@@ -12308,7 +12302,7 @@
         <v>2</v>
       </c>
       <c r="V140" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="W140" s="1">
         <v>45427</v>
@@ -12367,7 +12361,7 @@
         <v>1</v>
       </c>
       <c r="V141" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="W141" s="1">
         <v>45376</v>
@@ -12435,7 +12429,7 @@
         <v>1</v>
       </c>
       <c r="V142" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="W142" s="1">
         <v>45385</v>
@@ -12503,7 +12497,7 @@
         <v>1</v>
       </c>
       <c r="V143" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="W143" s="1">
         <v>45260</v>
@@ -12571,7 +12565,7 @@
         <v>1</v>
       </c>
       <c r="V144" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="W144" s="1">
         <v>45224</v>
@@ -12639,7 +12633,7 @@
         <v>2</v>
       </c>
       <c r="V145" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="W145" s="1">
         <v>45223</v>
@@ -12707,7 +12701,7 @@
         <v>2</v>
       </c>
       <c r="V146" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="W146" s="1">
         <v>45389</v>
@@ -12775,7 +12769,7 @@
         <v>5</v>
       </c>
       <c r="V147" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="W147" s="1">
         <v>45395</v>
@@ -12843,7 +12837,7 @@
         <v>1</v>
       </c>
       <c r="V148" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="W148" s="1">
         <v>45402</v>
@@ -12911,7 +12905,7 @@
         <v>1</v>
       </c>
       <c r="V149" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="W149" s="1">
         <v>45402</v>
@@ -12979,7 +12973,7 @@
         <v>1</v>
       </c>
       <c r="V150" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="W150" s="1">
         <v>45405</v>
@@ -13047,7 +13041,7 @@
         <v>1</v>
       </c>
       <c r="V151" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="W151" s="1">
         <v>45389</v>
@@ -13115,7 +13109,7 @@
         <v>1</v>
       </c>
       <c r="V152" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="W152" s="1">
         <v>45399</v>
@@ -13183,7 +13177,7 @@
         <v>2</v>
       </c>
       <c r="V153" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="W153" s="1">
         <v>45195</v>
@@ -13251,7 +13245,7 @@
         <v>1</v>
       </c>
       <c r="V154" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="W154" s="1">
         <v>45388</v>
@@ -13319,7 +13313,7 @@
         <v>1</v>
       </c>
       <c r="V155" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="W155" s="1">
         <v>45405</v>
@@ -13387,7 +13381,7 @@
         <v>1</v>
       </c>
       <c r="V156" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="W156" s="1">
         <v>45399</v>
@@ -13455,7 +13449,7 @@
         <v>1</v>
       </c>
       <c r="V157" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="W157" s="1">
         <v>45399</v>
@@ -13523,7 +13517,7 @@
         <v>1</v>
       </c>
       <c r="V158" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="W158" s="1">
         <v>45400</v>
@@ -13591,7 +13585,7 @@
         <v>1</v>
       </c>
       <c r="V159" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="W159" s="1">
         <v>45400</v>
@@ -13659,7 +13653,7 @@
         <v>1</v>
       </c>
       <c r="V160" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="W160" s="1">
         <v>45385</v>
@@ -13727,7 +13721,7 @@
         <v>1</v>
       </c>
       <c r="V161" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="W161" s="1">
         <v>45133</v>
@@ -13795,7 +13789,7 @@
         <v>1</v>
       </c>
       <c r="V162" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="W162" s="1">
         <v>45134</v>
@@ -13862,11 +13856,11 @@
       <c r="T163">
         <v>1</v>
       </c>
-      <c r="U163" t="s">
-        <v>508</v>
+      <c r="U163">
+        <v>1</v>
       </c>
       <c r="V163" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="W163" s="1">
         <v>45390</v>
@@ -13934,7 +13928,7 @@
         <v>1</v>
       </c>
       <c r="V164" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="W164" s="1">
         <v>45389</v>
@@ -14002,7 +13996,7 @@
         <v>1</v>
       </c>
       <c r="V165" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="W165" s="1">
         <v>45138</v>
@@ -14070,7 +14064,7 @@
         <v>2</v>
       </c>
       <c r="V166" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="W166" s="1">
         <v>45191</v>
@@ -14138,7 +14132,7 @@
         <v>3</v>
       </c>
       <c r="V167" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="W167" s="1">
         <v>45133</v>
@@ -14206,7 +14200,7 @@
         <v>1</v>
       </c>
       <c r="V168" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="W168" s="1">
         <v>45133</v>
@@ -14274,7 +14268,7 @@
         <v>3</v>
       </c>
       <c r="V169" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="W169" s="1">
         <v>45509</v>
@@ -14342,7 +14336,7 @@
         <v>1</v>
       </c>
       <c r="V170" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="W170" s="1">
         <v>45129</v>
@@ -14410,7 +14404,7 @@
         <v>1</v>
       </c>
       <c r="V171" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="W171" s="1">
         <v>45128</v>
@@ -14478,7 +14472,7 @@
         <v>1</v>
       </c>
       <c r="V172" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="W172" s="1">
         <v>45072</v>
@@ -14546,7 +14540,7 @@
         <v>1</v>
       </c>
       <c r="V173" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="W173" s="1">
         <v>45065</v>
@@ -14614,7 +14608,7 @@
         <v>1</v>
       </c>
       <c r="V174" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="W174" s="1">
         <v>45047</v>
@@ -14682,7 +14676,7 @@
         <v>1</v>
       </c>
       <c r="V175" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="W175" s="1">
         <v>45033</v>
@@ -14750,7 +14744,7 @@
         <v>1</v>
       </c>
       <c r="V176" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="W176" s="1">
         <v>44987</v>
@@ -14818,7 +14812,7 @@
         <v>1</v>
       </c>
       <c r="V177" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="W177" s="1">
         <v>44987</v>
@@ -14886,7 +14880,7 @@
         <v>9</v>
       </c>
       <c r="V178" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="W178" s="1">
         <v>44988</v>
@@ -14954,7 +14948,7 @@
         <v>1</v>
       </c>
       <c r="V179" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="W179" s="1">
         <v>44988</v>
@@ -15022,7 +15016,7 @@
         <v>3</v>
       </c>
       <c r="V180" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="W180" s="1">
         <v>44953</v>
@@ -15090,7 +15084,7 @@
         <v>1</v>
       </c>
       <c r="V181" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="W181" s="1">
         <v>44980</v>
@@ -15158,7 +15152,7 @@
         <v>1</v>
       </c>
       <c r="V182" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="W182" s="1">
         <v>44985</v>
@@ -15226,7 +15220,7 @@
         <v>1</v>
       </c>
       <c r="V183" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="W183" s="1">
         <v>44980</v>
@@ -15294,7 +15288,7 @@
         <v>2</v>
       </c>
       <c r="V184" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="W184" s="1">
         <v>44984</v>
@@ -15362,7 +15356,7 @@
         <v>1</v>
       </c>
       <c r="V185" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="W185" s="1">
         <v>44980</v>
@@ -15430,7 +15424,7 @@
         <v>1</v>
       </c>
       <c r="V186" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="W186" s="1">
         <v>44974</v>
@@ -15498,7 +15492,7 @@
         <v>2</v>
       </c>
       <c r="V187" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="W187" s="1">
         <v>44953</v>
@@ -15566,7 +15560,7 @@
         <v>4</v>
       </c>
       <c r="V188" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="W188" s="1">
         <v>44984</v>
@@ -15634,7 +15628,7 @@
         <v>1</v>
       </c>
       <c r="V189" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="W189" s="1">
         <v>44985</v>
@@ -15702,7 +15696,7 @@
         <v>1</v>
       </c>
       <c r="V190" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="W190" s="1">
         <v>44984</v>
@@ -15770,7 +15764,7 @@
         <v>5</v>
       </c>
       <c r="V191" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="W191" s="1">
         <v>44981</v>
@@ -15838,7 +15832,7 @@
         <v>1</v>
       </c>
       <c r="V192" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="W192" s="1">
         <v>44982</v>
@@ -15906,7 +15900,7 @@
         <v>5</v>
       </c>
       <c r="V193" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="W193" s="1">
         <v>44984</v>
@@ -15974,7 +15968,7 @@
         <v>1</v>
       </c>
       <c r="V194" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="W194" s="1">
         <v>44984</v>
@@ -16042,7 +16036,7 @@
         <v>4</v>
       </c>
       <c r="V195" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="W195" s="1">
         <v>44984</v>
@@ -16110,7 +16104,7 @@
         <v>2</v>
       </c>
       <c r="V196" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="W196" s="1">
         <v>44984</v>
@@ -16178,7 +16172,7 @@
         <v>2</v>
       </c>
       <c r="V197" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="W197" s="1">
         <v>44985</v>
@@ -16246,7 +16240,7 @@
         <v>11</v>
       </c>
       <c r="V198" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="W198" s="1">
         <v>45000</v>
@@ -16314,7 +16308,7 @@
         <v>1</v>
       </c>
       <c r="V199" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="W199" s="1">
         <v>44912</v>
@@ -16382,7 +16376,7 @@
         <v>5</v>
       </c>
       <c r="V200" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="W200" s="1">
         <v>44984</v>
@@ -16450,7 +16444,7 @@
         <v>4</v>
       </c>
       <c r="V201" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="W201" s="1">
         <v>44984</v>
@@ -16518,7 +16512,7 @@
         <v>1</v>
       </c>
       <c r="V202" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="W202" s="1">
         <v>45033</v>
@@ -16586,7 +16580,7 @@
         <v>1</v>
       </c>
       <c r="V203" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="W203" s="1">
         <v>44912</v>
@@ -16654,7 +16648,7 @@
         <v>1</v>
       </c>
       <c r="V204" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="W204" s="1">
         <v>44981</v>
@@ -16722,7 +16716,7 @@
         <v>1</v>
       </c>
       <c r="V205" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="W205" s="1">
         <v>44909</v>
@@ -16790,7 +16784,7 @@
         <v>1</v>
       </c>
       <c r="V206" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W206" s="1">
         <v>45033</v>
@@ -16858,7 +16852,7 @@
         <v>1</v>
       </c>
       <c r="V207" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="W207" s="1">
         <v>44988</v>
@@ -16926,7 +16920,7 @@
         <v>1</v>
       </c>
       <c r="V208" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="W208" s="1">
         <v>44980</v>
@@ -16994,7 +16988,7 @@
         <v>1</v>
       </c>
       <c r="V209" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="W209" s="1">
         <v>45033</v>
@@ -17062,7 +17056,7 @@
         <v>1</v>
       </c>
       <c r="V210" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="W210" s="1">
         <v>44988</v>
@@ -17130,7 +17124,7 @@
         <v>1</v>
       </c>
       <c r="V211" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="W211" s="1">
         <v>44988</v>
@@ -17198,7 +17192,7 @@
         <v>1</v>
       </c>
       <c r="V212" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="W212" s="1">
         <v>44988</v>
@@ -17266,7 +17260,7 @@
         <v>1</v>
       </c>
       <c r="V213" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="W213" s="1">
         <v>45033</v>
@@ -17333,11 +17327,11 @@
       <c r="T214">
         <v>1</v>
       </c>
-      <c r="U214" t="s">
-        <v>508</v>
+      <c r="U214">
+        <v>1</v>
       </c>
       <c r="V214" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="W214" s="1">
         <v>44988</v>
@@ -17405,7 +17399,7 @@
         <v>1</v>
       </c>
       <c r="V215" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="W215" s="1">
         <v>45033</v>
@@ -17473,7 +17467,7 @@
         <v>1</v>
       </c>
       <c r="V216" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="W216" s="1">
         <v>45427</v>
@@ -17541,7 +17535,7 @@
         <v>1</v>
       </c>
       <c r="V217" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="W217" s="1">
         <v>45128</v>
@@ -17609,7 +17603,7 @@
         <v>1</v>
       </c>
       <c r="V218" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="W218" s="1">
         <v>44982</v>
@@ -17677,7 +17671,7 @@
         <v>1</v>
       </c>
       <c r="V219" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="W219" s="1">
         <v>44733</v>
@@ -17745,7 +17739,7 @@
         <v>1</v>
       </c>
       <c r="V220" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="W220" s="1">
         <v>44729</v>
@@ -17813,7 +17807,7 @@
         <v>3</v>
       </c>
       <c r="V221" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="W221" s="1">
         <v>44718</v>
@@ -17881,7 +17875,7 @@
         <v>1</v>
       </c>
       <c r="V222" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="W222" s="1">
         <v>44718</v>
@@ -17949,7 +17943,7 @@
         <v>2</v>
       </c>
       <c r="V223" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="W223" s="1">
         <v>44717</v>
@@ -18017,7 +18011,7 @@
         <v>1</v>
       </c>
       <c r="V224" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="W224" s="1">
         <v>44614</v>
@@ -18085,7 +18079,7 @@
         <v>1</v>
       </c>
       <c r="V225" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="W225" s="1">
         <v>44617</v>
@@ -18153,7 +18147,7 @@
         <v>1</v>
       </c>
       <c r="V226" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="W226" s="1">
         <v>44615</v>
@@ -18221,7 +18215,7 @@
         <v>1</v>
       </c>
       <c r="V227" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="W227" s="1">
         <v>44614</v>
@@ -18289,7 +18283,7 @@
         <v>1</v>
       </c>
       <c r="V228" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="W228" s="1">
         <v>44614</v>
@@ -18357,7 +18351,7 @@
         <v>1</v>
       </c>
       <c r="V229" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="W229" s="1">
         <v>44615</v>
@@ -18425,7 +18419,7 @@
         <v>1</v>
       </c>
       <c r="V230" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="W230" s="1">
         <v>44615</v>
@@ -18493,7 +18487,7 @@
         <v>3</v>
       </c>
       <c r="V231" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="W231" s="1">
         <v>44578</v>
@@ -18561,7 +18555,7 @@
         <v>13</v>
       </c>
       <c r="V232" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="W232" s="1">
         <v>44578</v>
@@ -18629,7 +18623,7 @@
         <v>30</v>
       </c>
       <c r="V233" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="W233" s="1">
         <v>44578</v>
@@ -18697,7 +18691,7 @@
         <v>1</v>
       </c>
       <c r="V234" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="W234" s="1">
         <v>44578</v>
@@ -18765,7 +18759,7 @@
         <v>13</v>
       </c>
       <c r="V235" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="W235" s="1">
         <v>44578</v>
@@ -18833,7 +18827,7 @@
         <v>6</v>
       </c>
       <c r="V236" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="W236" s="1">
         <v>44578</v>
@@ -18900,11 +18894,11 @@
       <c r="T237">
         <v>1</v>
       </c>
-      <c r="U237" t="s">
-        <v>508</v>
+      <c r="U237">
+        <v>1</v>
       </c>
       <c r="V237" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="W237" s="1">
         <v>44591</v>
@@ -18972,7 +18966,7 @@
         <v>1</v>
       </c>
       <c r="V238" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="W238" s="1">
         <v>44591</v>
@@ -19040,7 +19034,7 @@
         <v>1</v>
       </c>
       <c r="V239" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="W239" s="1">
         <v>44591</v>
@@ -19108,7 +19102,7 @@
         <v>1</v>
       </c>
       <c r="V240" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="W240" s="1">
         <v>44582</v>
@@ -19176,7 +19170,7 @@
         <v>1</v>
       </c>
       <c r="V241" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="W241" s="1">
         <v>44582</v>
@@ -19243,11 +19237,11 @@
       <c r="T242">
         <v>3</v>
       </c>
-      <c r="U242" t="s">
-        <v>508</v>
+      <c r="U242">
+        <v>1</v>
       </c>
       <c r="V242" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="W242" s="1">
         <v>44582</v>
@@ -19315,7 +19309,7 @@
         <v>1</v>
       </c>
       <c r="V243" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="W243" s="1">
         <v>44587</v>
@@ -19383,7 +19377,7 @@
         <v>1</v>
       </c>
       <c r="V244" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="W244" s="1">
         <v>44587</v>
@@ -19451,7 +19445,7 @@
         <v>1</v>
       </c>
       <c r="V245" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="W245" s="1">
         <v>44528</v>
@@ -19519,7 +19513,7 @@
         <v>1</v>
       </c>
       <c r="V246" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="W246" s="1">
         <v>44591</v>
@@ -19587,7 +19581,7 @@
         <v>1</v>
       </c>
       <c r="V247" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="W247" s="1">
         <v>44591</v>
@@ -19649,7 +19643,7 @@
         <v>1</v>
       </c>
       <c r="V248" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="W248" s="1">
         <v>44591</v>
@@ -19717,7 +19711,7 @@
         <v>3</v>
       </c>
       <c r="V249" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="W249" s="1">
         <v>44591</v>
@@ -19785,7 +19779,7 @@
         <v>1</v>
       </c>
       <c r="V250" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="W250" s="1">
         <v>44591</v>
@@ -19853,7 +19847,7 @@
         <v>1</v>
       </c>
       <c r="V251" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="W251" s="1">
         <v>44591</v>
@@ -19921,7 +19915,7 @@
         <v>1</v>
       </c>
       <c r="V252" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="W252" s="1">
         <v>44591</v>
@@ -19989,7 +19983,7 @@
         <v>1</v>
       </c>
       <c r="V253" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="W253" s="1">
         <v>44591</v>
@@ -20057,7 +20051,7 @@
         <v>5</v>
       </c>
       <c r="V254" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="W254" s="1">
         <v>44589</v>
@@ -20124,11 +20118,11 @@
       <c r="T255">
         <v>2</v>
       </c>
-      <c r="U255" t="s">
-        <v>509</v>
+      <c r="U255">
+        <v>2</v>
       </c>
       <c r="V255" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="W255" s="1">
         <v>44588</v>
@@ -20196,7 +20190,7 @@
         <v>1</v>
       </c>
       <c r="V256" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="W256" s="1">
         <v>44588</v>
@@ -20264,7 +20258,7 @@
         <v>1</v>
       </c>
       <c r="V257" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="W257" s="1">
         <v>44588</v>
@@ -20332,7 +20326,7 @@
         <v>1</v>
       </c>
       <c r="V258" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="W258" s="1">
         <v>44640</v>
@@ -20400,7 +20394,7 @@
         <v>1</v>
       </c>
       <c r="V259" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="W259" s="1">
         <v>44640</v>
@@ -20468,7 +20462,7 @@
         <v>1</v>
       </c>
       <c r="V260" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="W260" s="1">
         <v>44413</v>
@@ -20536,7 +20530,7 @@
         <v>1</v>
       </c>
       <c r="V261" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="W261" s="1">
         <v>44588</v>
@@ -20604,7 +20598,7 @@
         <v>1</v>
       </c>
       <c r="V262" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="W262" s="1">
         <v>44590</v>
@@ -20672,7 +20666,7 @@
         <v>3</v>
       </c>
       <c r="V263" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="W263" s="1">
         <v>44640</v>
@@ -20740,7 +20734,7 @@
         <v>2</v>
       </c>
       <c r="V264" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="W264" s="1">
         <v>44591</v>
@@ -20808,7 +20802,7 @@
         <v>1</v>
       </c>
       <c r="V265" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="W265" s="1">
         <v>44591</v>
@@ -20876,7 +20870,7 @@
         <v>2</v>
       </c>
       <c r="V266" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="W266" s="1">
         <v>44591</v>
@@ -20943,11 +20937,11 @@
       <c r="T267">
         <v>1</v>
       </c>
-      <c r="U267" t="s">
-        <v>508</v>
+      <c r="U267">
+        <v>1</v>
       </c>
       <c r="V267" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="W267" s="1">
         <v>44591</v>
@@ -21015,7 +21009,7 @@
         <v>1</v>
       </c>
       <c r="V268" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="W268" s="1">
         <v>44643</v>
@@ -21083,7 +21077,7 @@
         <v>2</v>
       </c>
       <c r="V269" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="W269" s="1">
         <v>44643</v>
@@ -21151,7 +21145,7 @@
         <v>1</v>
       </c>
       <c r="V270" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="W270" s="1">
         <v>44590</v>
@@ -21219,7 +21213,7 @@
         <v>1</v>
       </c>
       <c r="V271" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="W271" s="1">
         <v>44590</v>
@@ -21287,7 +21281,7 @@
         <v>1</v>
       </c>
       <c r="V272" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="W272" s="1">
         <v>44641</v>
@@ -21355,7 +21349,7 @@
         <v>1</v>
       </c>
       <c r="V273" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="W273" s="1">
         <v>44591</v>
@@ -21423,7 +21417,7 @@
         <v>1</v>
       </c>
       <c r="V274" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="W274" s="1">
         <v>44641</v>
@@ -21491,7 +21485,7 @@
         <v>1</v>
       </c>
       <c r="V275" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="W275" s="1">
         <v>44588</v>
@@ -21559,7 +21553,7 @@
         <v>1</v>
       </c>
       <c r="V276" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="W276" s="1">
         <v>44588</v>
@@ -21627,7 +21621,7 @@
         <v>1</v>
       </c>
       <c r="V277" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="W277" s="1">
         <v>44588</v>
@@ -21695,7 +21689,7 @@
         <v>1</v>
       </c>
       <c r="V278" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="W278" s="1">
         <v>44588</v>
@@ -21763,7 +21757,7 @@
         <v>1</v>
       </c>
       <c r="V279" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="W279" s="1">
         <v>44588</v>
@@ -21831,7 +21825,7 @@
         <v>1</v>
       </c>
       <c r="V280" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="W280" s="1">
         <v>44588</v>
@@ -21899,7 +21893,7 @@
         <v>1</v>
       </c>
       <c r="V281" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="W281" s="1">
         <v>44588</v>
@@ -21967,7 +21961,7 @@
         <v>1</v>
       </c>
       <c r="V282" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="W282" s="1">
         <v>44588</v>
@@ -22035,7 +22029,7 @@
         <v>1</v>
       </c>
       <c r="V283" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="W283" s="1">
         <v>44587</v>
@@ -22103,7 +22097,7 @@
         <v>1</v>
       </c>
       <c r="V284" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="W284" s="1">
         <v>44587</v>
@@ -22171,7 +22165,7 @@
         <v>5</v>
       </c>
       <c r="V285" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="W285" s="1">
         <v>44592</v>
@@ -22239,7 +22233,7 @@
         <v>1</v>
       </c>
       <c r="V286" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="W286" s="1">
         <v>44592</v>
@@ -22307,7 +22301,7 @@
         <v>1</v>
       </c>
       <c r="V287" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="W287" s="1">
         <v>44586</v>
@@ -22375,7 +22369,7 @@
         <v>1</v>
       </c>
       <c r="V288" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="W288" s="1">
         <v>44586</v>
@@ -22443,7 +22437,7 @@
         <v>1</v>
       </c>
       <c r="V289" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="W289" s="1">
         <v>44586</v>
@@ -22511,7 +22505,7 @@
         <v>1</v>
       </c>
       <c r="V290" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="W290" s="1">
         <v>44586</v>
@@ -22579,7 +22573,7 @@
         <v>1</v>
       </c>
       <c r="V291" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="W291" s="1">
         <v>44582</v>
@@ -22647,7 +22641,7 @@
         <v>1</v>
       </c>
       <c r="V292" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="W292" s="1">
         <v>44582</v>
@@ -22715,7 +22709,7 @@
         <v>6</v>
       </c>
       <c r="V293" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="W293" s="1">
         <v>44591</v>
@@ -22783,7 +22777,7 @@
         <v>2</v>
       </c>
       <c r="V294" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="W294" s="1">
         <v>44589</v>
@@ -22851,7 +22845,7 @@
         <v>1</v>
       </c>
       <c r="V295" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="W295" s="1">
         <v>45727</v>
@@ -22919,7 +22913,7 @@
         <v>1</v>
       </c>
       <c r="V296" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="W296" s="1">
         <v>44582</v>
@@ -22987,7 +22981,7 @@
         <v>1</v>
       </c>
       <c r="V297" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="W297" s="1">
         <v>44371</v>
@@ -23055,7 +23049,7 @@
         <v>1</v>
       </c>
       <c r="V298" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="W298" s="1">
         <v>44370</v>
@@ -23123,7 +23117,7 @@
         <v>1</v>
       </c>
       <c r="V299" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="W299" s="1">
         <v>44370</v>
@@ -23191,7 +23185,7 @@
         <v>1</v>
       </c>
       <c r="V300" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="W300" s="1">
         <v>44370</v>
@@ -23259,7 +23253,7 @@
         <v>1</v>
       </c>
       <c r="V301" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="W301" s="1">
         <v>44356</v>
@@ -23327,7 +23321,7 @@
         <v>2</v>
       </c>
       <c r="V302" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="W302" s="1">
         <v>44236</v>
@@ -23395,7 +23389,7 @@
         <v>1</v>
       </c>
       <c r="V303" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="W303" s="1">
         <v>44155</v>
@@ -23463,7 +23457,7 @@
         <v>1</v>
       </c>
       <c r="V304" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="W304" s="1">
         <v>44154</v>
@@ -23531,7 +23525,7 @@
         <v>1</v>
       </c>
       <c r="V305" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="W305" s="1">
         <v>44149</v>
@@ -23599,7 +23593,7 @@
         <v>2</v>
       </c>
       <c r="V306" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="W306" s="1">
         <v>44109</v>
@@ -23667,7 +23661,7 @@
         <v>1</v>
       </c>
       <c r="V307" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="W307" s="1">
         <v>44107</v>
@@ -23735,7 +23729,7 @@
         <v>1</v>
       </c>
       <c r="V308" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="W308" s="1">
         <v>44095</v>
@@ -23803,7 +23797,7 @@
         <v>1</v>
       </c>
       <c r="V309" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="W309" s="1">
         <v>44095</v>
